--- a/excel_templates/Bill of Lading.xlsx
+++ b/excel_templates/Bill of Lading.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="15105" windowHeight="8070"/>
+    <workbookView windowWidth="18330" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="提货单" sheetId="16" r:id="rId1"/>
@@ -32,10 +32,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
   <si>
-    <t>{{Proxy client}}</t>
+    <t>{{Proxy_client}}</t>
   </si>
   <si>
-    <t>{{customs declaration}}</t>
+    <t>{{customs_declaration}}</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -128,10 +128,10 @@
     </r>
   </si>
   <si>
-    <t>{{Contract No.}}</t>
+    <t>{{Contract_No.}}</t>
   </si>
   <si>
-    <t>{{Bill of Lading Number}}</t>
+    <t>{{Bill_of_Lading_Number}}</t>
   </si>
   <si>
     <t>备    注</t>
@@ -2103,7 +2103,7 @@
       <c r="G31" s="55"/>
       <c r="H31" s="69">
         <f ca="1">TODAY()</f>
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="I31" s="7"/>
       <c r="J31" s="7"/>

--- a/excel_templates/Bill of Lading.xlsx
+++ b/excel_templates/Bill of Lading.xlsx
@@ -128,7 +128,7 @@
     </r>
   </si>
   <si>
-    <t>{{Contract_No.}}</t>
+    <t>{{Contract_No}}</t>
   </si>
   <si>
     <t>{{Bill_of_Lading_Number}}</t>
@@ -2103,7 +2103,7 @@
       <c r="G31" s="55"/>
       <c r="H31" s="69">
         <f ca="1">TODAY()</f>
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="I31" s="7"/>
       <c r="J31" s="7"/>
